--- a/templates/risk_register.xlsx
+++ b/templates/risk_register.xlsx
@@ -766,7 +766,7 @@
       </c>
       <c r="P2" s="4" t="inlineStr">
         <is>
-          <t>2027-03-20</t>
+          <t>2027-03-21</t>
         </is>
       </c>
       <c r="Q2" s="4" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="P3" s="11" t="inlineStr">
         <is>
-          <t>2027-03-20</t>
+          <t>2027-03-21</t>
         </is>
       </c>
       <c r="Q3" s="11" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>2027-03-20</t>
+          <t>2027-03-21</t>
         </is>
       </c>
       <c r="Q4" s="4" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="P5" s="11" t="inlineStr">
         <is>
-          <t>2027-03-20</t>
+          <t>2027-03-21</t>
         </is>
       </c>
       <c r="Q5" s="11" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>2027-03-20</t>
+          <t>2027-03-21</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
